--- a/光伏配储项目/电价数据/2026/莲花峰厂.xlsx
+++ b/光伏配储项目/电价数据/2026/莲花峰厂.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.316</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27642</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.26767</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.25868</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25443</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.27475</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.26424</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.24138</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.15892</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.15866</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.19778</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.22728</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17545</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26655</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.26961</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26963</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22086</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.2011</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.28198</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.84678</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.47313</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5395800000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.17963</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.07519</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.82543</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.01644</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.99388</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7482000000000001</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.9686699999999999</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.44589</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.4513</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.4695299999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.0509</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.44667</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.4698</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.45728</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.332</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.4386</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.12763</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.19444</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.61386</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.5518</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.19073</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.17237</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.19673</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.08766</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.03865</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.95469</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.81932</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.59211</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.43106</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.83497</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.44871</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.32735</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.7426200000000001</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.7537999999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.76375</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.26018</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.16562</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.1863</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.23825</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.44067</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.07618999999999999</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45037</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.49869</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.49452</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.49578</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5133</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.43852</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.51279</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.69252</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.41854</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.4968</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.44254</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.41484</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.332</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.45417</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48976</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.47914</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.05736</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.27203</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.8065</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.11065</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.09222</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.10657</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.27926</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.04676</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19954</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.11461</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.03122</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.10396</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6606300000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5022799999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.26178</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>-0.01566</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.28405</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13347</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.01594</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.29786</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.28248</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.29752</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26464</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25429</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22973</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.09559999999999999</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.26948</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.03171</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27489</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31849</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.10029</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.24821</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.05558</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.08745</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.29036</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19804</v>
+      </c>
+      <c r="L122" t="n">
+        <v>-0.01922</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.03006</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25503</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.04829</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.08292000000000001</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.03322</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21921</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19738</v>
+      </c>
+      <c r="W122" t="n">
+        <v>-0.02013</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17949</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20631</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26888</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04789</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04924</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00424</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20176</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04453</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27133</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.18935</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.005900000000000001</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05483</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05483</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14031</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31693</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.7006699999999999</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.16984</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22474</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.05819</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15669</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7709</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92031</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91412</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8630599999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29609</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88742</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63152</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18698</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87029</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6575599999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33078</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03284</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53074</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57382</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2071</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62191</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5384</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45589</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43721</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.44871</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.49792</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.45802</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.61541</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87898</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29174</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.2114</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.28877</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29498</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18434</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26409</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26397</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27655</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26379</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27635</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3252</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.7794500000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.20777</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.20357</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29882</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.30035</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.28133</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.07881999999999999</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>-0.01929</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.07715000000000001</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.01887</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.008109999999999999</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.0835</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.01879</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.27559</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.03395</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.44945</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.11156</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.01919</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>-0.01318</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-0.01912</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>-0.01689</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-0.01684</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.02897</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.03017</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.02873</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>-0.02909</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.07169</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>-0.01701</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>-0.02189</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>-0.0173</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>-0.01877</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>-0.01721</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>-0.00759</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>-0.01963</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>-0.0181</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>-0.01768</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>-0.01499</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>-0.01942</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>-0.0173</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>-0.01692</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>-0.01639</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>-0.01661</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.08404</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>-0.01703</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>-0.00646</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>-0.01526</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>-0.01242</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>-0.01835</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>-0.01475</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.21812</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>-0.01692</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>-0.0174</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>-0.01625</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>-0.03301</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.00221</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-0.00419</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-0.00707</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.03158</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-0.0326</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-0.01722</v>
+      </c>
+      <c r="L126" t="n">
+        <v>-0.01308</v>
+      </c>
+      <c r="M126" t="n">
+        <v>-0.01208</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-0.01862</v>
+      </c>
+      <c r="O126" t="n">
+        <v>-0.01834</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.09208</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>-0.01462</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.08473</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.0498</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.10719</v>
+      </c>
+      <c r="U126" t="n">
+        <v>-0.01618</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.25384</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>-0.04443</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.04079</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.20874</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.25903</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.15218</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.23498</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.07309</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.14968</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.24123</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.20415</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.00566</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.03447</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.02971</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.27571</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.24158</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.27908</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.24376</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.20491</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.20001</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.21864</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.05741</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.06961000000000001</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.12405</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.13822</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.06768</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.20571</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.08153000000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>-0.0166</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.05201</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.02697</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.07459</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.11227</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.02979</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.03929</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.19906</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.04382</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.23928</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.24659</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>-0.0297</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.04332</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.06545000000000001</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.08755</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.08724</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.08465</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.08687</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.08053</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.06736</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.07856999999999999</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.07806999999999999</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.07104000000000001</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.06773</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.08631999999999999</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.08084999999999999</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.08601</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>-0.01469</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.08591</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.28029</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.09979</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.08192000000000001</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.23831</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.0674</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.22825</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>-0.02134</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.06994</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.06195000000000001</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.03206000000000001</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.02928</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.05154</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19409</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.03659</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.19113</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.02734</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.05338</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.06039</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.06011</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.07304000000000001</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.0716</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.03688</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.03986</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.04394</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.06981</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.03902000000000001</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.19621</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.03934</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.02173</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.02093</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.03778</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.06598999999999999</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.17098</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.03109</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.14248</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.02993</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.25012</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.01443</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-0.02268</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.14726</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.07992</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.06794</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.06703000000000001</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.12961</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.24937</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.06845</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.06328</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.18235</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.13078</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.06362</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.05569</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.17925</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.19795</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26731</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.23425</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.27875</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.28633</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.27406</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.21787</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.27736</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.27904</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.26756</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.25543</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.27521</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.27607</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.27396</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.27522</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.27535</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.28722</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.27015</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.26824</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25382</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28471</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29786</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.28637</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26122</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.26389</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.42871</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30526</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.29354</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.39652</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.00772</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.40568</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6227999999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.48018</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49957</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44372</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42442</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.40304</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.54067</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27824</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.19693</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.42233</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.19379</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.19567</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43058</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.40935</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.52634</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41428</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.41814</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.42143</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.11435</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.10152</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>-0.005889999999999999</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.009939999999999999</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.43247</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.41852</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>-0.01127</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.14963</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.61258</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.09334999999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.45766</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.08857999999999999</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.10041</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.04817</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.08331000000000001</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.24538</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>-0.02538</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28767</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>-0.02536</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.28266</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.20295</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.27307</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27635</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27989</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28014</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20514</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19539</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.26934</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27767</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27598</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.2679</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27543</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19811</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19565</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.16072</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23854</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.20008</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.00017</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19565</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20172</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20858</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17467</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16607</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.16887</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.20486</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.23907</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.21255</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.26563</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.24605</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.24625</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.24924</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.22917</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.23206</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.20898</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.19837</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.23944</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.22234</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.27294</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.23898</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.20172</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.19636</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.06876</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.18752</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.19948</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.2302</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.2548</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.15239</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.2479</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.27431</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.2284</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.26194</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.27366</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27443</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28842</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.27896</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.28024</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.22039</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.21089</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.28389</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>-0.00057</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.01484</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.24031</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.319</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28442</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.00103</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28714</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28298</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27656</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27652</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28689</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.5483899999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.51522</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29939</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41281</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44533</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49894</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.58685</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.55802</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59333</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.74229</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.38713</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46899</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42863</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31628</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.43507</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42627</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>8.000000000000001e-05</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.20902</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.27311</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.02982</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.21962</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.20903</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.27335</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.29891</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6481</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.3292</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41133</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27987</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.01435</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.2814700000000001</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.28647</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.18567</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.00012</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.28672</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.19089</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.03537</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.25621</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.00937</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04503</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>-0.04839</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.04758</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.20002</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.19996</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.03498</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.00017</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.00036</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>-0.03289</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.19963</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.19825</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.19883</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.19851</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>-0.04226</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.27948</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.26355</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.20033</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.22265</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.09809</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.26149</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>-0.01865</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>-0.02734</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>-0.02729</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>-0.02542</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.05686</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.0489</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>-0.02764</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.28589</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.17587</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.00658</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.00728</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>-0.03537</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>-0.0432</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>-0.02839</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>-0.02803</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.11788</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.28373</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.18091</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.11291</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.18319</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.27008</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.20279</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.17476</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.01505</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.23768</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.01151</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17431</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.00105</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20546</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17477</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.16409</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.00049</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.16634</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.16915</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17196</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.00749</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17477</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.00731</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.01671</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18775</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15629</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.24008</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.03852000000000001</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24472</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.05857</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.19817</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.10563</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.14319</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.26154</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.02177</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.25433</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.19754</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.16643</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.01446</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.007480000000000001</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.00038</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.00273</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.19977</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.1965</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.13484</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.01545</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.00435</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.01329</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.01071</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.008400000000000001</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.01353</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.01563</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.01478</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.17553</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.00916</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.00142</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.20564</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.15712</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.2003</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.03329</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.12164</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.15576</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.01428</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>-0.03893</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.02863</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.01406</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>-0.03555</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22137</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.01957</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25141</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.20801</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.2318</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.22831</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.0992</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.10877</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.23178</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.08001000000000001</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.20777</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.02954</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.02233</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.20025</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.21569</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.23772</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.25487</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28245</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.05558</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.19266</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18937</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.27134</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.00115</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20816</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22832</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.2184</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.04407</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.01211</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.00113</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.00113</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.0005600000000000001</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.0005600000000000001</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.20099</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.01261</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.0005600000000000001</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.00062</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.18111</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.01208</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.01212</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.00192</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.00325</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24552</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.03698</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00666</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-7.000000000000001e-05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02166</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02675</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03881</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04436</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.22852</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.10695</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20559</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.20727</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.21267</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.20757</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.18909</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.24509</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25883</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.24815</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.27737</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.24016</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27203</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.03327</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.1772</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17169</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.17613</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.02031</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.16947</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.15789</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.01959</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.0487</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.02178</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.01904</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.008840000000000001</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.01096</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.01492</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.20062</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.20024</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.04885</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.04708</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08470999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.00311</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25538</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28379</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.46646</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00012</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00169</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06665</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29784</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47061</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.65278</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.5007699999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.42621</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7347400000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.78786</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.5628099999999999</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.61514</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.71128</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.71128</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.7102200000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.78639</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.43074</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31264</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.44034</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.27577</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26913</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26292</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25958</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25131</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.22113</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.26878</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.20827</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.17506</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20378</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.16948</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.02028</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.16772</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.19004</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.23969</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27155</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.26998</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.22087</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.23891</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.22786</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26328</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.40428</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.2966</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29643</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.2028</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.44666</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41141</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.45723</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.27971</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.72749</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.74663</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40854</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.49913</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.64907</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.74663</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.41099</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42396</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29644</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.58056</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.75798</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.66365</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55501</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32692</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28914</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.01896</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29349</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28758</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.25571</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19575</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.41441</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.53149</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.13418</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.18007</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.4607</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.33237</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.66314</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41946</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.20002</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.01027</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.00099</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.17634</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.26416</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.18237</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.11441</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.34173</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-0.04973</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.23008</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17909</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29704</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14638</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14204</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.11623</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22594</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14601</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14332</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18853</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.26907</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22999</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.03384</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.0395</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22999</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.10358</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.20397</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.02989</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.04865999999999999</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.21307</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.12692</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.22801</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.27972</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.21911</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.15558</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.12475</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.25875</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.20092</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.01441</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>-0.00012</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.25534</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.00584</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.26744</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.333</v>
       </c>
     </row>
   </sheetData>
